--- a/tools/coolin-sizing.xlsx
+++ b/tools/coolin-sizing.xlsx
@@ -268,7 +268,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>IF(B12&lt;=2.0,1850,IF(B12&lt;=2.5,1850,IF(B12&lt;=3.5,1995,IF(B12&lt;=5.0,2280,IF(B12&lt;=6.0,2650,IF(B12&lt;=7.1,2950,""))))))</f>
+        <f>IF(B12&lt;=2.0,1650,IF(B12&lt;=2.5,1650,IF(B12&lt;=3.5,1995,IF(B12&lt;=5.0,2280,IF(B12&lt;=6.0,2650,IF(B12&lt;=7.1,2950,""))))))</f>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -402,7 +402,7 @@
         <f>IF(J18="","",IF(J18&lt;=2.0,2.0,IF(J18&lt;=2.5,2.5,IF(J18&lt;=3.5,3.5,IF(J18&lt;=5.0,5.0,IF(J18&lt;=6.0,6.0,IF(J18&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L18" s="6">
-        <f>IF(J18="","",IF(J18&lt;=2.0,1850,IF(J18&lt;=2.5,1850,IF(J18&lt;=3.5,1995,IF(J18&lt;=5.0,2280,IF(J18&lt;=6.0,2650,IF(J18&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J18="","",IF(J18&lt;=2.0,1650,IF(J18&lt;=2.5,1650,IF(J18&lt;=3.5,1995,IF(J18&lt;=5.0,2280,IF(J18&lt;=6.0,2650,IF(J18&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="19">
@@ -450,7 +450,7 @@
         <f>IF(J19="","",IF(J19&lt;=2.0,2.0,IF(J19&lt;=2.5,2.5,IF(J19&lt;=3.5,3.5,IF(J19&lt;=5.0,5.0,IF(J19&lt;=6.0,6.0,IF(J19&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L19" s="6">
-        <f>IF(J19="","",IF(J19&lt;=2.0,1850,IF(J19&lt;=2.5,1850,IF(J19&lt;=3.5,1995,IF(J19&lt;=5.0,2280,IF(J19&lt;=6.0,2650,IF(J19&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J19="","",IF(J19&lt;=2.0,1650,IF(J19&lt;=2.5,1650,IF(J19&lt;=3.5,1995,IF(J19&lt;=5.0,2280,IF(J19&lt;=6.0,2650,IF(J19&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="20">
@@ -498,7 +498,7 @@
         <f>IF(J20="","",IF(J20&lt;=2.0,2.0,IF(J20&lt;=2.5,2.5,IF(J20&lt;=3.5,3.5,IF(J20&lt;=5.0,5.0,IF(J20&lt;=6.0,6.0,IF(J20&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L20" s="6">
-        <f>IF(J20="","",IF(J20&lt;=2.0,1850,IF(J20&lt;=2.5,1850,IF(J20&lt;=3.5,1995,IF(J20&lt;=5.0,2280,IF(J20&lt;=6.0,2650,IF(J20&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J20="","",IF(J20&lt;=2.0,1650,IF(J20&lt;=2.5,1650,IF(J20&lt;=3.5,1995,IF(J20&lt;=5.0,2280,IF(J20&lt;=6.0,2650,IF(J20&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="21">
@@ -520,7 +520,7 @@
         <f>IF(J21="","",IF(J21&lt;=2.0,2.0,IF(J21&lt;=2.5,2.5,IF(J21&lt;=3.5,3.5,IF(J21&lt;=5.0,5.0,IF(J21&lt;=6.0,6.0,IF(J21&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L21" s="6">
-        <f>IF(J21="","",IF(J21&lt;=2.0,1850,IF(J21&lt;=2.5,1850,IF(J21&lt;=3.5,1995,IF(J21&lt;=5.0,2280,IF(J21&lt;=6.0,2650,IF(J21&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J21="","",IF(J21&lt;=2.0,1650,IF(J21&lt;=2.5,1650,IF(J21&lt;=3.5,1995,IF(J21&lt;=5.0,2280,IF(J21&lt;=6.0,2650,IF(J21&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="22">
@@ -542,7 +542,7 @@
         <f>IF(J22="","",IF(J22&lt;=2.0,2.0,IF(J22&lt;=2.5,2.5,IF(J22&lt;=3.5,3.5,IF(J22&lt;=5.0,5.0,IF(J22&lt;=6.0,6.0,IF(J22&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L22" s="6">
-        <f>IF(J22="","",IF(J22&lt;=2.0,1850,IF(J22&lt;=2.5,1850,IF(J22&lt;=3.5,1995,IF(J22&lt;=5.0,2280,IF(J22&lt;=6.0,2650,IF(J22&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J22="","",IF(J22&lt;=2.0,1650,IF(J22&lt;=2.5,1650,IF(J22&lt;=3.5,1995,IF(J22&lt;=5.0,2280,IF(J22&lt;=6.0,2650,IF(J22&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="23">
@@ -564,7 +564,7 @@
         <f>IF(J23="","",IF(J23&lt;=2.0,2.0,IF(J23&lt;=2.5,2.5,IF(J23&lt;=3.5,3.5,IF(J23&lt;=5.0,5.0,IF(J23&lt;=6.0,6.0,IF(J23&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L23" s="6">
-        <f>IF(J23="","",IF(J23&lt;=2.0,1850,IF(J23&lt;=2.5,1850,IF(J23&lt;=3.5,1995,IF(J23&lt;=5.0,2280,IF(J23&lt;=6.0,2650,IF(J23&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J23="","",IF(J23&lt;=2.0,1650,IF(J23&lt;=2.5,1650,IF(J23&lt;=3.5,1995,IF(J23&lt;=5.0,2280,IF(J23&lt;=6.0,2650,IF(J23&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="24">
@@ -586,7 +586,7 @@
         <f>IF(J24="","",IF(J24&lt;=2.0,2.0,IF(J24&lt;=2.5,2.5,IF(J24&lt;=3.5,3.5,IF(J24&lt;=5.0,5.0,IF(J24&lt;=6.0,6.0,IF(J24&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L24" s="6">
-        <f>IF(J24="","",IF(J24&lt;=2.0,1850,IF(J24&lt;=2.5,1850,IF(J24&lt;=3.5,1995,IF(J24&lt;=5.0,2280,IF(J24&lt;=6.0,2650,IF(J24&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J24="","",IF(J24&lt;=2.0,1650,IF(J24&lt;=2.5,1650,IF(J24&lt;=3.5,1995,IF(J24&lt;=5.0,2280,IF(J24&lt;=6.0,2650,IF(J24&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="25">
@@ -608,7 +608,7 @@
         <f>IF(J25="","",IF(J25&lt;=2.0,2.0,IF(J25&lt;=2.5,2.5,IF(J25&lt;=3.5,3.5,IF(J25&lt;=5.0,5.0,IF(J25&lt;=6.0,6.0,IF(J25&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L25" s="6">
-        <f>IF(J25="","",IF(J25&lt;=2.0,1850,IF(J25&lt;=2.5,1850,IF(J25&lt;=3.5,1995,IF(J25&lt;=5.0,2280,IF(J25&lt;=6.0,2650,IF(J25&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J25="","",IF(J25&lt;=2.0,1650,IF(J25&lt;=2.5,1650,IF(J25&lt;=3.5,1995,IF(J25&lt;=5.0,2280,IF(J25&lt;=6.0,2650,IF(J25&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="26">
@@ -630,7 +630,7 @@
         <f>IF(J26="","",IF(J26&lt;=2.0,2.0,IF(J26&lt;=2.5,2.5,IF(J26&lt;=3.5,3.5,IF(J26&lt;=5.0,5.0,IF(J26&lt;=6.0,6.0,IF(J26&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L26" s="6">
-        <f>IF(J26="","",IF(J26&lt;=2.0,1850,IF(J26&lt;=2.5,1850,IF(J26&lt;=3.5,1995,IF(J26&lt;=5.0,2280,IF(J26&lt;=6.0,2650,IF(J26&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J26="","",IF(J26&lt;=2.0,1650,IF(J26&lt;=2.5,1650,IF(J26&lt;=3.5,1995,IF(J26&lt;=5.0,2280,IF(J26&lt;=6.0,2650,IF(J26&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="27">
@@ -652,7 +652,7 @@
         <f>IF(J27="","",IF(J27&lt;=2.0,2.0,IF(J27&lt;=2.5,2.5,IF(J27&lt;=3.5,3.5,IF(J27&lt;=5.0,5.0,IF(J27&lt;=6.0,6.0,IF(J27&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L27" s="6">
-        <f>IF(J27="","",IF(J27&lt;=2.0,1850,IF(J27&lt;=2.5,1850,IF(J27&lt;=3.5,1995,IF(J27&lt;=5.0,2280,IF(J27&lt;=6.0,2650,IF(J27&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J27="","",IF(J27&lt;=2.0,1650,IF(J27&lt;=2.5,1650,IF(J27&lt;=3.5,1995,IF(J27&lt;=5.0,2280,IF(J27&lt;=6.0,2650,IF(J27&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="28">
@@ -674,7 +674,7 @@
         <f>IF(J28="","",IF(J28&lt;=2.0,2.0,IF(J28&lt;=2.5,2.5,IF(J28&lt;=3.5,3.5,IF(J28&lt;=5.0,5.0,IF(J28&lt;=6.0,6.0,IF(J28&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L28" s="6">
-        <f>IF(J28="","",IF(J28&lt;=2.0,1850,IF(J28&lt;=2.5,1850,IF(J28&lt;=3.5,1995,IF(J28&lt;=5.0,2280,IF(J28&lt;=6.0,2650,IF(J28&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J28="","",IF(J28&lt;=2.0,1650,IF(J28&lt;=2.5,1650,IF(J28&lt;=3.5,1995,IF(J28&lt;=5.0,2280,IF(J28&lt;=6.0,2650,IF(J28&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="29">
@@ -696,7 +696,7 @@
         <f>IF(J29="","",IF(J29&lt;=2.0,2.0,IF(J29&lt;=2.5,2.5,IF(J29&lt;=3.5,3.5,IF(J29&lt;=5.0,5.0,IF(J29&lt;=6.0,6.0,IF(J29&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L29" s="6">
-        <f>IF(J29="","",IF(J29&lt;=2.0,1850,IF(J29&lt;=2.5,1850,IF(J29&lt;=3.5,1995,IF(J29&lt;=5.0,2280,IF(J29&lt;=6.0,2650,IF(J29&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J29="","",IF(J29&lt;=2.0,1650,IF(J29&lt;=2.5,1650,IF(J29&lt;=3.5,1995,IF(J29&lt;=5.0,2280,IF(J29&lt;=6.0,2650,IF(J29&lt;=7.1,2950,"")))))))</f>
       </c>
     </row>
     <row r="30">

--- a/tools/coolin-sizing.xlsx
+++ b/tools/coolin-sizing.xlsx
@@ -268,7 +268,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>IF(B12&lt;=2.0,1650,IF(B12&lt;=2.5,1650,IF(B12&lt;=3.5,1995,IF(B12&lt;=5.0,2280,IF(B12&lt;=6.0,2650,IF(B12&lt;=7.1,2950,""))))))</f>
+        <f>IF(B12&lt;=2.0,1650,IF(B12&lt;=2.5,1650,IF(B12&lt;=3.5,1850,IF(B12&lt;=5.0,2150,IF(B12&lt;=6.0,2450,IF(B12&lt;=7.1,2750,""))))))</f>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -402,7 +402,7 @@
         <f>IF(J18="","",IF(J18&lt;=2.0,2.0,IF(J18&lt;=2.5,2.5,IF(J18&lt;=3.5,3.5,IF(J18&lt;=5.0,5.0,IF(J18&lt;=6.0,6.0,IF(J18&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L18" s="6">
-        <f>IF(J18="","",IF(J18&lt;=2.0,1650,IF(J18&lt;=2.5,1650,IF(J18&lt;=3.5,1995,IF(J18&lt;=5.0,2280,IF(J18&lt;=6.0,2650,IF(J18&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J18="","",IF(J18&lt;=2.0,1650,IF(J18&lt;=2.5,1650,IF(J18&lt;=3.5,1850,IF(J18&lt;=5.0,2150,IF(J18&lt;=6.0,2450,IF(J18&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="19">
@@ -450,7 +450,7 @@
         <f>IF(J19="","",IF(J19&lt;=2.0,2.0,IF(J19&lt;=2.5,2.5,IF(J19&lt;=3.5,3.5,IF(J19&lt;=5.0,5.0,IF(J19&lt;=6.0,6.0,IF(J19&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L19" s="6">
-        <f>IF(J19="","",IF(J19&lt;=2.0,1650,IF(J19&lt;=2.5,1650,IF(J19&lt;=3.5,1995,IF(J19&lt;=5.0,2280,IF(J19&lt;=6.0,2650,IF(J19&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J19="","",IF(J19&lt;=2.0,1650,IF(J19&lt;=2.5,1650,IF(J19&lt;=3.5,1850,IF(J19&lt;=5.0,2150,IF(J19&lt;=6.0,2450,IF(J19&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="20">
@@ -498,7 +498,7 @@
         <f>IF(J20="","",IF(J20&lt;=2.0,2.0,IF(J20&lt;=2.5,2.5,IF(J20&lt;=3.5,3.5,IF(J20&lt;=5.0,5.0,IF(J20&lt;=6.0,6.0,IF(J20&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L20" s="6">
-        <f>IF(J20="","",IF(J20&lt;=2.0,1650,IF(J20&lt;=2.5,1650,IF(J20&lt;=3.5,1995,IF(J20&lt;=5.0,2280,IF(J20&lt;=6.0,2650,IF(J20&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J20="","",IF(J20&lt;=2.0,1650,IF(J20&lt;=2.5,1650,IF(J20&lt;=3.5,1850,IF(J20&lt;=5.0,2150,IF(J20&lt;=6.0,2450,IF(J20&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="21">
@@ -520,7 +520,7 @@
         <f>IF(J21="","",IF(J21&lt;=2.0,2.0,IF(J21&lt;=2.5,2.5,IF(J21&lt;=3.5,3.5,IF(J21&lt;=5.0,5.0,IF(J21&lt;=6.0,6.0,IF(J21&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L21" s="6">
-        <f>IF(J21="","",IF(J21&lt;=2.0,1650,IF(J21&lt;=2.5,1650,IF(J21&lt;=3.5,1995,IF(J21&lt;=5.0,2280,IF(J21&lt;=6.0,2650,IF(J21&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J21="","",IF(J21&lt;=2.0,1650,IF(J21&lt;=2.5,1650,IF(J21&lt;=3.5,1850,IF(J21&lt;=5.0,2150,IF(J21&lt;=6.0,2450,IF(J21&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="22">
@@ -542,7 +542,7 @@
         <f>IF(J22="","",IF(J22&lt;=2.0,2.0,IF(J22&lt;=2.5,2.5,IF(J22&lt;=3.5,3.5,IF(J22&lt;=5.0,5.0,IF(J22&lt;=6.0,6.0,IF(J22&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L22" s="6">
-        <f>IF(J22="","",IF(J22&lt;=2.0,1650,IF(J22&lt;=2.5,1650,IF(J22&lt;=3.5,1995,IF(J22&lt;=5.0,2280,IF(J22&lt;=6.0,2650,IF(J22&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J22="","",IF(J22&lt;=2.0,1650,IF(J22&lt;=2.5,1650,IF(J22&lt;=3.5,1850,IF(J22&lt;=5.0,2150,IF(J22&lt;=6.0,2450,IF(J22&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="23">
@@ -564,7 +564,7 @@
         <f>IF(J23="","",IF(J23&lt;=2.0,2.0,IF(J23&lt;=2.5,2.5,IF(J23&lt;=3.5,3.5,IF(J23&lt;=5.0,5.0,IF(J23&lt;=6.0,6.0,IF(J23&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L23" s="6">
-        <f>IF(J23="","",IF(J23&lt;=2.0,1650,IF(J23&lt;=2.5,1650,IF(J23&lt;=3.5,1995,IF(J23&lt;=5.0,2280,IF(J23&lt;=6.0,2650,IF(J23&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J23="","",IF(J23&lt;=2.0,1650,IF(J23&lt;=2.5,1650,IF(J23&lt;=3.5,1850,IF(J23&lt;=5.0,2150,IF(J23&lt;=6.0,2450,IF(J23&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="24">
@@ -586,7 +586,7 @@
         <f>IF(J24="","",IF(J24&lt;=2.0,2.0,IF(J24&lt;=2.5,2.5,IF(J24&lt;=3.5,3.5,IF(J24&lt;=5.0,5.0,IF(J24&lt;=6.0,6.0,IF(J24&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L24" s="6">
-        <f>IF(J24="","",IF(J24&lt;=2.0,1650,IF(J24&lt;=2.5,1650,IF(J24&lt;=3.5,1995,IF(J24&lt;=5.0,2280,IF(J24&lt;=6.0,2650,IF(J24&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J24="","",IF(J24&lt;=2.0,1650,IF(J24&lt;=2.5,1650,IF(J24&lt;=3.5,1850,IF(J24&lt;=5.0,2150,IF(J24&lt;=6.0,2450,IF(J24&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="25">
@@ -608,7 +608,7 @@
         <f>IF(J25="","",IF(J25&lt;=2.0,2.0,IF(J25&lt;=2.5,2.5,IF(J25&lt;=3.5,3.5,IF(J25&lt;=5.0,5.0,IF(J25&lt;=6.0,6.0,IF(J25&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L25" s="6">
-        <f>IF(J25="","",IF(J25&lt;=2.0,1650,IF(J25&lt;=2.5,1650,IF(J25&lt;=3.5,1995,IF(J25&lt;=5.0,2280,IF(J25&lt;=6.0,2650,IF(J25&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J25="","",IF(J25&lt;=2.0,1650,IF(J25&lt;=2.5,1650,IF(J25&lt;=3.5,1850,IF(J25&lt;=5.0,2150,IF(J25&lt;=6.0,2450,IF(J25&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="26">
@@ -630,7 +630,7 @@
         <f>IF(J26="","",IF(J26&lt;=2.0,2.0,IF(J26&lt;=2.5,2.5,IF(J26&lt;=3.5,3.5,IF(J26&lt;=5.0,5.0,IF(J26&lt;=6.0,6.0,IF(J26&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L26" s="6">
-        <f>IF(J26="","",IF(J26&lt;=2.0,1650,IF(J26&lt;=2.5,1650,IF(J26&lt;=3.5,1995,IF(J26&lt;=5.0,2280,IF(J26&lt;=6.0,2650,IF(J26&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J26="","",IF(J26&lt;=2.0,1650,IF(J26&lt;=2.5,1650,IF(J26&lt;=3.5,1850,IF(J26&lt;=5.0,2150,IF(J26&lt;=6.0,2450,IF(J26&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="27">
@@ -652,7 +652,7 @@
         <f>IF(J27="","",IF(J27&lt;=2.0,2.0,IF(J27&lt;=2.5,2.5,IF(J27&lt;=3.5,3.5,IF(J27&lt;=5.0,5.0,IF(J27&lt;=6.0,6.0,IF(J27&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L27" s="6">
-        <f>IF(J27="","",IF(J27&lt;=2.0,1650,IF(J27&lt;=2.5,1650,IF(J27&lt;=3.5,1995,IF(J27&lt;=5.0,2280,IF(J27&lt;=6.0,2650,IF(J27&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J27="","",IF(J27&lt;=2.0,1650,IF(J27&lt;=2.5,1650,IF(J27&lt;=3.5,1850,IF(J27&lt;=5.0,2150,IF(J27&lt;=6.0,2450,IF(J27&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="28">
@@ -674,7 +674,7 @@
         <f>IF(J28="","",IF(J28&lt;=2.0,2.0,IF(J28&lt;=2.5,2.5,IF(J28&lt;=3.5,3.5,IF(J28&lt;=5.0,5.0,IF(J28&lt;=6.0,6.0,IF(J28&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L28" s="6">
-        <f>IF(J28="","",IF(J28&lt;=2.0,1650,IF(J28&lt;=2.5,1650,IF(J28&lt;=3.5,1995,IF(J28&lt;=5.0,2280,IF(J28&lt;=6.0,2650,IF(J28&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J28="","",IF(J28&lt;=2.0,1650,IF(J28&lt;=2.5,1650,IF(J28&lt;=3.5,1850,IF(J28&lt;=5.0,2150,IF(J28&lt;=6.0,2450,IF(J28&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="29">
@@ -696,7 +696,7 @@
         <f>IF(J29="","",IF(J29&lt;=2.0,2.0,IF(J29&lt;=2.5,2.5,IF(J29&lt;=3.5,3.5,IF(J29&lt;=5.0,5.0,IF(J29&lt;=6.0,6.0,IF(J29&lt;=7.1,7.1,"two units")))))))</f>
       </c>
       <c r="L29" s="6">
-        <f>IF(J29="","",IF(J29&lt;=2.0,1650,IF(J29&lt;=2.5,1650,IF(J29&lt;=3.5,1995,IF(J29&lt;=5.0,2280,IF(J29&lt;=6.0,2650,IF(J29&lt;=7.1,2950,"")))))))</f>
+        <f>IF(J29="","",IF(J29&lt;=2.0,1650,IF(J29&lt;=2.5,1650,IF(J29&lt;=3.5,1850,IF(J29&lt;=5.0,2150,IF(J29&lt;=6.0,2450,IF(J29&lt;=7.1,2750,"")))))))</f>
       </c>
     </row>
     <row r="30">
